--- a/tiflow-xborder/fhir-error-codes/1.0.0-draft/ValueSet-tiflow-xborder-operation-outcome-details-vs.xlsx
+++ b/tiflow-xborder/fhir-error-codes/1.0.0-draft/ValueSet-tiflow-xborder-operation-outcome-details-vs.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t>Property</t>
   </si>
@@ -119,40 +119,76 @@
     <t>TIFLOW_AUTH_ROLE_NOT_ALLOWED</t>
   </si>
   <si>
+    <t>Access role not allowed</t>
+  </si>
+  <si>
     <t>TIFLOW_CONSENT_REQUIRED</t>
   </si>
   <si>
+    <t>Consent required</t>
+  </si>
+  <si>
     <t>TIFLOW_ACCESS_PERMISSION_INVALID</t>
   </si>
   <si>
+    <t>Access permission invalid</t>
+  </si>
+  <si>
     <t>TIFLOW_AUTH_NOT_OWNER</t>
   </si>
   <si>
+    <t>Authenticated actor is not owner</t>
+  </si>
+  <si>
     <t>TIFLOW_ACCESSCODE_MISMATCH</t>
   </si>
   <si>
+    <t>Access code mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_STATUS_MISMATCH</t>
   </si>
   <si>
+    <t>Task status mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_TASK_ID_REQUIRED</t>
   </si>
   <si>
+    <t>Task id required</t>
+  </si>
+  <si>
     <t>TIFLOW_KVNR_MISMATCH</t>
   </si>
   <si>
+    <t>KVNR mismatch</t>
+  </si>
+  <si>
     <t>TIFLOW_CONSENT_MISSING</t>
   </si>
   <si>
+    <t>Consent missing</t>
+  </si>
+  <si>
     <t>TIFLOW_ACCESS_CODE_INVALID</t>
   </si>
   <si>
+    <t>Access code invalid</t>
+  </si>
+  <si>
     <t>https://gematik.de/fhir/tiflow/core/CodeSystem/tiflow-operation-outcome-details-cs</t>
   </si>
   <si>
     <t>SVC_VALIDATION_FAILED</t>
   </si>
   <si>
+    <t>FHIR Profile Validation Failed</t>
+  </si>
+  <si>
     <t>SVC_TELEMATIKID_TEMPORARILY_BLOCKED</t>
+  </si>
+  <si>
+    <t>The specified Telematik-ID is temporarily blocked</t>
   </si>
   <si>
     <t>https://gematik.de/fhir/ti/CodeSystem/operation-outcome-details-codes</t>
@@ -476,61 +512,81 @@
       <c r="A2" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>50</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
@@ -545,7 +601,7 @@
         <v>30</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -572,15 +628,19 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B2" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>57</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
@@ -595,7 +655,7 @@
         <v>30</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
